--- a/artfynd/S 5154-2024 artfynd.xlsx
+++ b/artfynd/S 5154-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -795,6 +800,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112133458</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -911,6 +921,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/271591</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1027,6 +1042,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/395605</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1133,6 +1153,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107408825</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1249,6 +1274,11 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI)</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/690777</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1355,8 +1385,21 @@
           <t>Skogsstyrelsens Nyckelbiotopsinventering (NBI) 2009-2021</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107408826</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 5154-2024 artfynd.xlsx
+++ b/artfynd/S 5154-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1388,6 +1388,220 @@
       <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/107408826</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135666139</v>
+      </c>
+      <c r="B8" t="n">
+        <v>108424</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221530</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Hampflockel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Eupatorium cannabinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kädarp NO, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>460707</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6221088</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kiaby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135666139</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135666177</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104248</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221987</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsbingel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Mercurialis perennis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kädarp NO, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>460707</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6221088</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kiaby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135666177</t>
         </is>
       </c>
     </row>
@@ -1399,6 +1613,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 5154-2024 artfynd.xlsx
+++ b/artfynd/S 5154-2024 artfynd.xlsx
@@ -1396,7 +1396,7 @@
         <v>135666139</v>
       </c>
       <c r="B8" t="n">
-        <v>108424</v>
+        <v>108451</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135666177</v>
       </c>
       <c r="B9" t="n">
-        <v>104248</v>
+        <v>104275</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 5154-2024 artfynd.xlsx
+++ b/artfynd/S 5154-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1388,6 +1388,220 @@
       <c r="AZ7" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/107408826</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>135666139</v>
+      </c>
+      <c r="B8" t="n">
+        <v>108456</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221530</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Hampflockel</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Eupatorium cannabinum</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Kädarp NO, Sk</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>460707</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6221088</v>
+      </c>
+      <c r="S8" t="n">
+        <v>25</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Kiaby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135666139</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>135666177</v>
+      </c>
+      <c r="B9" t="n">
+        <v>104280</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>221987</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Skogsbingel</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Mercurialis perennis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Kädarp NO, Sk</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>460707</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6221088</v>
+      </c>
+      <c r="S9" t="n">
+        <v>25</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kristianstad</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Kiaby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-08-05</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Hans Ingvarsson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135666177</t>
         </is>
       </c>
     </row>
@@ -1399,6 +1613,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 5154-2024 artfynd.xlsx
+++ b/artfynd/S 5154-2024 artfynd.xlsx
@@ -1396,7 +1396,7 @@
         <v>135666139</v>
       </c>
       <c r="B8" t="n">
-        <v>108456</v>
+        <v>108458</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135666177</v>
       </c>
       <c r="B9" t="n">
-        <v>104280</v>
+        <v>104282</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 5154-2024 artfynd.xlsx
+++ b/artfynd/S 5154-2024 artfynd.xlsx
@@ -1396,7 +1396,7 @@
         <v>135666139</v>
       </c>
       <c r="B8" t="n">
-        <v>108458</v>
+        <v>108481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135666177</v>
       </c>
       <c r="B9" t="n">
-        <v>104282</v>
+        <v>104302</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 5154-2024 artfynd.xlsx
+++ b/artfynd/S 5154-2024 artfynd.xlsx
@@ -1396,7 +1396,7 @@
         <v>135666139</v>
       </c>
       <c r="B8" t="n">
-        <v>108481</v>
+        <v>108483</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135666177</v>
       </c>
       <c r="B9" t="n">
-        <v>104302</v>
+        <v>104304</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 5154-2024 artfynd.xlsx
+++ b/artfynd/S 5154-2024 artfynd.xlsx
@@ -1396,7 +1396,7 @@
         <v>135666139</v>
       </c>
       <c r="B8" t="n">
-        <v>108483</v>
+        <v>108484</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135666177</v>
       </c>
       <c r="B9" t="n">
-        <v>104304</v>
+        <v>104305</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 5154-2024 artfynd.xlsx
+++ b/artfynd/S 5154-2024 artfynd.xlsx
@@ -1396,7 +1396,7 @@
         <v>135666139</v>
       </c>
       <c r="B8" t="n">
-        <v>108484</v>
+        <v>108485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135666177</v>
       </c>
       <c r="B9" t="n">
-        <v>104305</v>
+        <v>104306</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 5154-2024 artfynd.xlsx
+++ b/artfynd/S 5154-2024 artfynd.xlsx
@@ -1396,7 +1396,7 @@
         <v>135666139</v>
       </c>
       <c r="B8" t="n">
-        <v>108485</v>
+        <v>108491</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135666177</v>
       </c>
       <c r="B9" t="n">
-        <v>104306</v>
+        <v>104312</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/S 5154-2024 artfynd.xlsx
+++ b/artfynd/S 5154-2024 artfynd.xlsx
@@ -1396,7 +1396,7 @@
         <v>135666139</v>
       </c>
       <c r="B8" t="n">
-        <v>108491</v>
+        <v>108492</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>135666177</v>
       </c>
       <c r="B9" t="n">
-        <v>104312</v>
+        <v>104313</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
